--- a/입주율.xlsx
+++ b/입주율.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\입주율\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E71F238-5ACB-47C7-A501-0F98CA5DC230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D50BBEE-2296-4578-9302-7DA7EC518345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3038B8C-C650-4013-936F-29BC3C3EE88E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED758F3D-971B-47B5-9E66-227B2573ABCB}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1959,7 +1959,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10442400-8D65-4DE4-AA26-1A0B42E2B735}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7293CCD-5903-428C-B723-6DF3F44E7C4B}">
   <dimension ref="A1:BB267"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -3585,10 +3585,10 @@
         <v>45261</v>
       </c>
       <c r="E22">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F22" s="2">
-        <v>0.86060000000000003</v>
+        <v>0.86409999999999998</v>
       </c>
       <c r="H22">
         <v>41</v>
@@ -3657,7 +3657,7 @@
         <v>3</v>
       </c>
       <c r="AH22">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:53" x14ac:dyDescent="0.3">
@@ -3730,10 +3730,10 @@
         <v>45841</v>
       </c>
       <c r="E24">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="F24" s="2">
-        <v>0.96150000000000002</v>
+        <v>0.96819999999999995</v>
       </c>
       <c r="G24">
         <v>4</v>
@@ -3760,7 +3760,10 @@
         <v>7</v>
       </c>
       <c r="O24">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="P24">
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:53" x14ac:dyDescent="0.3">
@@ -3797,10 +3800,10 @@
         <v>45930</v>
       </c>
       <c r="E26">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="F26" s="2">
-        <v>0.48449999999999999</v>
+        <v>0.54349999999999998</v>
       </c>
       <c r="I26">
         <v>36</v>
@@ -3815,7 +3818,10 @@
         <v>21</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="N26">
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:53" x14ac:dyDescent="0.3">
@@ -4203,10 +4209,10 @@
         <v>45014</v>
       </c>
       <c r="E34">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F34" s="2">
-        <v>0.99570000000000003</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>14</v>
@@ -4261,6 +4267,9 @@
       </c>
       <c r="AO34">
         <v>2</v>
+      </c>
+      <c r="AQ34">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.3">
@@ -5044,10 +5053,10 @@
         <v>45182</v>
       </c>
       <c r="E45">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F45" s="2">
-        <v>0.99890000000000001</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>486</v>
@@ -5081,6 +5090,9 @@
       </c>
       <c r="U45">
         <v>2</v>
+      </c>
+      <c r="AL45">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.3">
@@ -5769,10 +5781,10 @@
         <v>45694</v>
       </c>
       <c r="E58">
-        <v>467</v>
+        <v>515</v>
       </c>
       <c r="F58" s="2">
-        <v>0.55789999999999995</v>
+        <v>0.61529999999999996</v>
       </c>
       <c r="L58">
         <v>53</v>
@@ -5799,7 +5811,10 @@
         <v>7</v>
       </c>
       <c r="T58">
-        <v>16</v>
+        <v>45</v>
+      </c>
+      <c r="U58">
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:43" x14ac:dyDescent="0.3">
@@ -5816,10 +5831,10 @@
         <v>45569</v>
       </c>
       <c r="E59">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F59" s="2">
-        <v>0.98370000000000002</v>
+        <v>0.98509999999999998</v>
       </c>
       <c r="G59">
         <v>8</v>
@@ -5864,6 +5879,9 @@
         <v>3</v>
       </c>
       <c r="V59">
+        <v>1</v>
+      </c>
+      <c r="X59">
         <v>1</v>
       </c>
     </row>
@@ -5881,10 +5899,10 @@
         <v>45608</v>
       </c>
       <c r="E60">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F60" s="2">
-        <v>0.92110000000000003</v>
+        <v>0.9254</v>
       </c>
       <c r="H60">
         <v>2</v>
@@ -5926,7 +5944,7 @@
         <v>2</v>
       </c>
       <c r="W60">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:43" x14ac:dyDescent="0.3">
@@ -5943,10 +5961,10 @@
         <v>45498</v>
       </c>
       <c r="E61">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="F61" s="2">
-        <v>0.87150000000000005</v>
+        <v>0.87909999999999999</v>
       </c>
       <c r="G61">
         <v>4</v>
@@ -6009,7 +6027,10 @@
         <v>6</v>
       </c>
       <c r="AA61">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="AB61">
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:43" x14ac:dyDescent="0.3">
@@ -6026,10 +6047,10 @@
         <v>45762</v>
       </c>
       <c r="E62">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="F62" s="2">
-        <v>0.69030000000000002</v>
+        <v>0.74299999999999999</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -6059,7 +6080,10 @@
         <v>27</v>
       </c>
       <c r="R62">
-        <v>20</v>
+        <v>44</v>
+      </c>
+      <c r="S62">
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:43" x14ac:dyDescent="0.3">
@@ -6076,10 +6100,10 @@
         <v>45877</v>
       </c>
       <c r="E63">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="F63" s="2">
-        <v>0.30740000000000001</v>
+        <v>0.33040000000000003</v>
       </c>
       <c r="I63">
         <v>54</v>
@@ -6097,7 +6121,10 @@
         <v>16</v>
       </c>
       <c r="N63">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="O63">
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:43" x14ac:dyDescent="0.3">
@@ -6380,10 +6407,10 @@
         <v>45393</v>
       </c>
       <c r="E68">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F68" s="2">
-        <v>0.99680000000000002</v>
+        <v>0.99780000000000002</v>
       </c>
       <c r="H68">
         <v>365</v>
@@ -6429,6 +6456,9 @@
       </c>
       <c r="AB68">
         <v>2</v>
+      </c>
+      <c r="AE68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:50" x14ac:dyDescent="0.3">
@@ -6977,10 +7007,10 @@
         <v>45183</v>
       </c>
       <c r="E77">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F77" s="2">
-        <v>0.93400000000000005</v>
+        <v>0.95050000000000001</v>
       </c>
       <c r="H77">
         <v>5</v>
@@ -7037,7 +7067,10 @@
         <v>3</v>
       </c>
       <c r="AK77">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="AL77">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:50" x14ac:dyDescent="0.3">
@@ -7252,10 +7285,10 @@
         <v>44985</v>
       </c>
       <c r="E81">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="F81" s="2">
-        <v>0.95689999999999997</v>
+        <v>0.96009999999999995</v>
       </c>
       <c r="H81">
         <v>43</v>
@@ -7330,7 +7363,10 @@
         <v>2</v>
       </c>
       <c r="AR81">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="AS81">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:51" x14ac:dyDescent="0.3">
@@ -7678,10 +7714,10 @@
         <v>44894</v>
       </c>
       <c r="E87">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F87" s="2">
-        <v>0.99680000000000002</v>
+        <v>0.99839999999999995</v>
       </c>
       <c r="H87">
         <v>10</v>
@@ -7765,6 +7801,9 @@
         <v>1</v>
       </c>
       <c r="AT87">
+        <v>1</v>
+      </c>
+      <c r="AU87">
         <v>1</v>
       </c>
     </row>
@@ -8128,10 +8167,10 @@
         <v>46006</v>
       </c>
       <c r="E93">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F93" s="2">
-        <v>4.1200000000000001E-2</v>
+        <v>8.1100000000000005E-2</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -8140,7 +8179,10 @@
         <v>22</v>
       </c>
       <c r="J93">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="K93">
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:51" x14ac:dyDescent="0.3">
@@ -8157,10 +8199,10 @@
         <v>45538</v>
       </c>
       <c r="E94">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F94" s="2">
-        <v>0.99399999999999999</v>
+        <v>0.99550000000000005</v>
       </c>
       <c r="G94">
         <v>46</v>
@@ -8218,6 +8260,9 @@
       </c>
       <c r="Y94">
         <v>3</v>
+      </c>
+      <c r="Z94">
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:51" x14ac:dyDescent="0.3">
@@ -8296,10 +8341,10 @@
         <v>45950</v>
       </c>
       <c r="E96">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="F96" s="2">
-        <v>0.28170000000000001</v>
+        <v>0.34589999999999999</v>
       </c>
       <c r="I96">
         <v>2</v>
@@ -8311,7 +8356,10 @@
         <v>65</v>
       </c>
       <c r="L96">
-        <v>22</v>
+        <v>43</v>
+      </c>
+      <c r="M96">
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:54" x14ac:dyDescent="0.3">
@@ -8496,10 +8544,10 @@
         <v>45602</v>
       </c>
       <c r="E100">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F100" s="2">
-        <v>0.74670000000000003</v>
+        <v>0.79479999999999995</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -8544,7 +8592,10 @@
         <v>20</v>
       </c>
       <c r="W100">
-        <v>8</v>
+        <v>16</v>
+      </c>
+      <c r="X100">
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:54" x14ac:dyDescent="0.3">
@@ -8561,10 +8612,10 @@
         <v>45623</v>
       </c>
       <c r="E101">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F101" s="2">
-        <v>0.95489999999999997</v>
+        <v>0.95660000000000001</v>
       </c>
       <c r="I101">
         <v>7</v>
@@ -8606,7 +8657,7 @@
         <v>2</v>
       </c>
       <c r="W101">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:54" x14ac:dyDescent="0.3">
@@ -8958,10 +9009,10 @@
         <v>45278</v>
       </c>
       <c r="E106">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F106" s="2">
-        <v>0.97060000000000002</v>
+        <v>0.97389999999999999</v>
       </c>
       <c r="H106">
         <v>13</v>
@@ -9022,6 +9073,9 @@
       </c>
       <c r="AG106">
         <v>2</v>
+      </c>
+      <c r="AH106">
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:54" x14ac:dyDescent="0.3">
@@ -9656,10 +9710,10 @@
         <v>45415</v>
       </c>
       <c r="E116">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F116" s="2">
-        <v>0.89129999999999998</v>
+        <v>0.89980000000000004</v>
       </c>
       <c r="H116">
         <v>2</v>
@@ -9722,7 +9776,10 @@
         <v>2</v>
       </c>
       <c r="AC116">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="AD116">
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:44" x14ac:dyDescent="0.3">
@@ -9739,10 +9796,10 @@
         <v>45432</v>
       </c>
       <c r="E117">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F117" s="2">
-        <v>0.96619999999999995</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="I117">
         <v>9</v>
@@ -9784,6 +9841,9 @@
         <v>1</v>
       </c>
       <c r="Z117">
+        <v>1</v>
+      </c>
+      <c r="AD117">
         <v>1</v>
       </c>
     </row>
@@ -9886,10 +9946,13 @@
         <v>46000</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F120" s="2">
-        <v>0</v>
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="K120">
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:44" x14ac:dyDescent="0.3">
@@ -9906,10 +9969,10 @@
         <v>45779</v>
       </c>
       <c r="E121">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="F121" s="2">
-        <v>0.61650000000000005</v>
+        <v>0.62039999999999995</v>
       </c>
       <c r="H121">
         <v>178</v>
@@ -9939,7 +10002,10 @@
         <v>6</v>
       </c>
       <c r="Q121">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="R121">
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:44" x14ac:dyDescent="0.3">
@@ -9985,10 +10051,10 @@
         <v>45636</v>
       </c>
       <c r="E123">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F123" s="2">
-        <v>0.92049999999999998</v>
+        <v>0.92330000000000001</v>
       </c>
       <c r="H123">
         <v>3</v>
@@ -10031,6 +10097,9 @@
       </c>
       <c r="U123">
         <v>3</v>
+      </c>
+      <c r="V123">
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:44" x14ac:dyDescent="0.3">
@@ -10493,10 +10562,10 @@
         <v>45160</v>
       </c>
       <c r="E131">
-        <v>1651</v>
+        <v>1654</v>
       </c>
       <c r="F131" s="2">
-        <v>0.99580000000000002</v>
+        <v>0.99760000000000004</v>
       </c>
       <c r="G131">
         <v>18</v>
@@ -10580,6 +10649,12 @@
         <v>1</v>
       </c>
       <c r="AJ131">
+        <v>1</v>
+      </c>
+      <c r="AL131">
+        <v>2</v>
+      </c>
+      <c r="AM131">
         <v>1</v>
       </c>
     </row>
@@ -11893,10 +11968,10 @@
         <v>44860</v>
       </c>
       <c r="E150">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F150" s="2">
-        <v>0.9375</v>
+        <v>0.94269999999999998</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -11995,7 +12070,7 @@
         <v>1</v>
       </c>
       <c r="AV150">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:48" x14ac:dyDescent="0.3">
@@ -12035,10 +12110,10 @@
         <v>45343</v>
       </c>
       <c r="E152">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="F152" s="2">
-        <v>0.98529999999999995</v>
+        <v>0.99350000000000005</v>
       </c>
       <c r="I152">
         <v>126</v>
@@ -12102,6 +12177,12 @@
       </c>
       <c r="AE152">
         <v>2</v>
+      </c>
+      <c r="AF152">
+        <v>2</v>
+      </c>
+      <c r="AG152">
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:48" x14ac:dyDescent="0.3">
@@ -12147,10 +12228,10 @@
         <v>45630</v>
       </c>
       <c r="E154">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="F154" s="2">
-        <v>0.9264</v>
+        <v>0.95350000000000001</v>
       </c>
       <c r="I154">
         <v>1</v>
@@ -12192,7 +12273,10 @@
         <v>6</v>
       </c>
       <c r="V154">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="W154">
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:48" x14ac:dyDescent="0.3">
@@ -12209,10 +12293,10 @@
         <v>45840</v>
       </c>
       <c r="E155">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="F155" s="2">
-        <v>0.37780000000000002</v>
+        <v>0.40670000000000001</v>
       </c>
       <c r="J155">
         <v>11</v>
@@ -12230,7 +12314,10 @@
         <v>21</v>
       </c>
       <c r="O155">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="P155">
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:48" x14ac:dyDescent="0.3">
@@ -12285,10 +12372,10 @@
         <v>45680</v>
       </c>
       <c r="E157">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F157" s="2">
-        <v>0.94059999999999999</v>
+        <v>0.94650000000000001</v>
       </c>
       <c r="J157">
         <v>101</v>
@@ -12324,6 +12411,9 @@
         <v>3</v>
       </c>
       <c r="U157">
+        <v>3</v>
+      </c>
+      <c r="V157">
         <v>1</v>
       </c>
     </row>
@@ -12364,10 +12454,10 @@
         <v>45426</v>
       </c>
       <c r="E159">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F159" s="2">
-        <v>0.8871</v>
+        <v>0.89249999999999996</v>
       </c>
       <c r="H159">
         <v>51</v>
@@ -12421,6 +12511,9 @@
         <v>3</v>
       </c>
       <c r="AB159">
+        <v>2</v>
+      </c>
+      <c r="AD159">
         <v>2</v>
       </c>
     </row>
@@ -12438,10 +12531,10 @@
         <v>45478</v>
       </c>
       <c r="E160">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F160" s="2">
-        <v>0.87180000000000002</v>
+        <v>0.92310000000000003</v>
       </c>
       <c r="H160">
         <v>3</v>
@@ -12489,6 +12582,9 @@
         <v>1</v>
       </c>
       <c r="AA160">
+        <v>2</v>
+      </c>
+      <c r="AB160">
         <v>1</v>
       </c>
     </row>
@@ -12583,10 +12679,10 @@
         <v>45915</v>
       </c>
       <c r="E162">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="F162" s="2">
-        <v>0.15240000000000001</v>
+        <v>0.21340000000000001</v>
       </c>
       <c r="K162">
         <v>2</v>
@@ -12595,7 +12691,10 @@
         <v>48</v>
       </c>
       <c r="M162">
-        <v>25</v>
+        <v>43</v>
+      </c>
+      <c r="N162">
+        <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:50" x14ac:dyDescent="0.3">
@@ -12697,10 +12796,10 @@
         <v>45569</v>
       </c>
       <c r="E165">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F165" s="2">
-        <v>0.39019999999999999</v>
+        <v>0.42280000000000001</v>
       </c>
       <c r="Q165">
         <v>1</v>
@@ -12724,7 +12823,7 @@
         <v>2</v>
       </c>
       <c r="X165">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:50" x14ac:dyDescent="0.3">
@@ -13174,10 +13273,10 @@
         <v>45161</v>
       </c>
       <c r="E174">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F174" s="2">
-        <v>0.99570000000000003</v>
+        <v>1</v>
       </c>
       <c r="G174">
         <v>2</v>
@@ -13237,6 +13336,9 @@
         <v>1</v>
       </c>
       <c r="AI174">
+        <v>1</v>
+      </c>
+      <c r="AL174">
         <v>1</v>
       </c>
     </row>
@@ -13650,10 +13752,10 @@
         <v>45341</v>
       </c>
       <c r="E181">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F181" s="2">
-        <v>0.96199999999999997</v>
+        <v>0.96350000000000002</v>
       </c>
       <c r="H181">
         <v>100</v>
@@ -13716,6 +13818,9 @@
         <v>1</v>
       </c>
       <c r="AD181">
+        <v>1</v>
+      </c>
+      <c r="AF181">
         <v>1</v>
       </c>
     </row>
@@ -14428,10 +14533,10 @@
         <v>44860</v>
       </c>
       <c r="E192">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F192" s="2">
-        <v>0.99370000000000003</v>
+        <v>1</v>
       </c>
       <c r="I192">
         <v>10</v>
@@ -14491,6 +14596,9 @@
         <v>1</v>
       </c>
       <c r="AU192">
+        <v>1</v>
+      </c>
+      <c r="AV192">
         <v>1</v>
       </c>
     </row>
@@ -14700,10 +14808,10 @@
         <v>45518</v>
       </c>
       <c r="E196">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F196" s="2">
-        <v>0.94640000000000002</v>
+        <v>0.95379999999999998</v>
       </c>
       <c r="I196">
         <v>49</v>
@@ -14755,6 +14863,9 @@
       </c>
       <c r="Y196">
         <v>6</v>
+      </c>
+      <c r="AA196">
+        <v>4</v>
       </c>
     </row>
     <row r="197" spans="1:49" x14ac:dyDescent="0.3">
@@ -14771,10 +14882,10 @@
         <v>45974</v>
       </c>
       <c r="E197">
-        <v>1342</v>
+        <v>1480</v>
       </c>
       <c r="F197" s="2">
-        <v>0.76339999999999997</v>
+        <v>0.84189999999999998</v>
       </c>
       <c r="I197">
         <v>711</v>
@@ -14783,7 +14894,10 @@
         <v>450</v>
       </c>
       <c r="K197">
-        <v>181</v>
+        <v>249</v>
+      </c>
+      <c r="L197">
+        <v>70</v>
       </c>
     </row>
     <row r="198" spans="1:49" x14ac:dyDescent="0.3">
@@ -14800,10 +14914,10 @@
         <v>45736</v>
       </c>
       <c r="E198">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="F198" s="2">
-        <v>0.33900000000000002</v>
+        <v>0.38179999999999997</v>
       </c>
       <c r="K198">
         <v>6</v>
@@ -14830,7 +14944,10 @@
         <v>22</v>
       </c>
       <c r="S198">
-        <v>12</v>
+        <v>23</v>
+      </c>
+      <c r="T198">
+        <v>4</v>
       </c>
     </row>
     <row r="199" spans="1:49" x14ac:dyDescent="0.3">
@@ -14847,16 +14964,19 @@
         <v>45987</v>
       </c>
       <c r="E199">
-        <v>141</v>
+        <v>275</v>
       </c>
       <c r="F199" s="2">
-        <v>0.1134</v>
+        <v>0.22120000000000001</v>
       </c>
       <c r="J199">
         <v>18</v>
       </c>
       <c r="K199">
-        <v>123</v>
+        <v>212</v>
+      </c>
+      <c r="L199">
+        <v>45</v>
       </c>
     </row>
     <row r="200" spans="1:49" x14ac:dyDescent="0.3">
@@ -15624,10 +15744,10 @@
         <v>45226</v>
       </c>
       <c r="E211">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F211" s="2">
-        <v>0.43530000000000002</v>
+        <v>0.4471</v>
       </c>
       <c r="G211">
         <v>1</v>
@@ -15714,7 +15834,7 @@
         <v>1</v>
       </c>
       <c r="AJ211">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:52" x14ac:dyDescent="0.3">
@@ -16609,10 +16729,10 @@
         <v>45932</v>
       </c>
       <c r="E225">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="F225" s="2">
-        <v>0.88249999999999995</v>
+        <v>0.90359999999999996</v>
       </c>
       <c r="H225">
         <v>53</v>
@@ -16627,7 +16747,10 @@
         <v>34</v>
       </c>
       <c r="L225">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="M225">
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:46" x14ac:dyDescent="0.3">
@@ -16644,10 +16767,10 @@
         <v>45932</v>
       </c>
       <c r="E226">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F226" s="2">
-        <v>0.87970000000000004</v>
+        <v>0.91139999999999999</v>
       </c>
       <c r="H226">
         <v>22</v>
@@ -16662,7 +16785,10 @@
         <v>9</v>
       </c>
       <c r="L226">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:46" x14ac:dyDescent="0.3">
@@ -16679,10 +16805,10 @@
         <v>45953</v>
       </c>
       <c r="E227">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="F227" s="2">
-        <v>0.40139999999999998</v>
+        <v>0.61219999999999997</v>
       </c>
       <c r="I227">
         <v>1</v>
@@ -16694,7 +16820,10 @@
         <v>21</v>
       </c>
       <c r="L227">
-        <v>14</v>
+        <v>37</v>
+      </c>
+      <c r="M227">
+        <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:46" x14ac:dyDescent="0.3">
@@ -16711,16 +16840,19 @@
         <v>45993</v>
       </c>
       <c r="E228">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="F228" s="2">
-        <v>0.32819999999999999</v>
+        <v>0.4945</v>
       </c>
       <c r="I228">
         <v>51</v>
       </c>
       <c r="J228">
-        <v>97</v>
+        <v>148</v>
+      </c>
+      <c r="K228">
+        <v>24</v>
       </c>
     </row>
     <row r="229" spans="1:46" x14ac:dyDescent="0.3">
@@ -16811,10 +16943,10 @@
         <v>45909</v>
       </c>
       <c r="E230">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="F230" s="2">
-        <v>0.36480000000000001</v>
+        <v>0.4133</v>
       </c>
       <c r="I230">
         <v>16</v>
@@ -16829,7 +16961,10 @@
         <v>21</v>
       </c>
       <c r="M230">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="N230">
+        <v>7</v>
       </c>
     </row>
     <row r="231" spans="1:46" x14ac:dyDescent="0.3">
@@ -17486,10 +17621,10 @@
         <v>45218</v>
       </c>
       <c r="E239">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F239" s="2">
-        <v>0.98939999999999995</v>
+        <v>0.99299999999999999</v>
       </c>
       <c r="G239">
         <v>11</v>
@@ -17576,6 +17711,9 @@
         <v>3</v>
       </c>
       <c r="AI239">
+        <v>2</v>
+      </c>
+      <c r="AK239">
         <v>2</v>
       </c>
     </row>
@@ -18466,10 +18604,10 @@
         <v>45343</v>
       </c>
       <c r="E252">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="F252" s="2">
-        <v>0.9859</v>
+        <v>0.98939999999999995</v>
       </c>
       <c r="H252">
         <v>1</v>
@@ -18539,6 +18677,12 @@
       </c>
       <c r="AD252">
         <v>3</v>
+      </c>
+      <c r="AF252">
+        <v>1</v>
+      </c>
+      <c r="AG252">
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:53" x14ac:dyDescent="0.3">
@@ -18601,10 +18745,16 @@
         <v>46031</v>
       </c>
       <c r="E255">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="F255" s="2">
-        <v>0</v>
+        <v>8.4699999999999998E-2</v>
+      </c>
+      <c r="I255">
+        <v>50</v>
+      </c>
+      <c r="J255">
+        <v>48</v>
       </c>
     </row>
     <row r="256" spans="1:53" x14ac:dyDescent="0.3">
@@ -18644,10 +18794,10 @@
         <v>45860</v>
       </c>
       <c r="E257">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="F257" s="2">
-        <v>0.96250000000000002</v>
+        <v>0.96689999999999998</v>
       </c>
       <c r="G257">
         <v>2</v>
@@ -18674,7 +18824,10 @@
         <v>17</v>
       </c>
       <c r="O257">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="P257">
+        <v>2</v>
       </c>
     </row>
     <row r="258" spans="1:54" x14ac:dyDescent="0.3">
@@ -18691,10 +18844,10 @@
         <v>45446</v>
       </c>
       <c r="E258">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="F258" s="2">
-        <v>0.95150000000000001</v>
+        <v>0.96260000000000001</v>
       </c>
       <c r="G258">
         <v>1</v>
@@ -18752,6 +18905,12 @@
       </c>
       <c r="AA258">
         <v>4</v>
+      </c>
+      <c r="AB258">
+        <v>3</v>
+      </c>
+      <c r="AC258">
+        <v>2</v>
       </c>
     </row>
     <row r="259" spans="1:54" x14ac:dyDescent="0.3">
@@ -18768,10 +18927,10 @@
         <v>45567</v>
       </c>
       <c r="E259">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="F259" s="2">
-        <v>0.83040000000000003</v>
+        <v>0.85460000000000003</v>
       </c>
       <c r="I259">
         <v>6</v>
@@ -18819,7 +18978,10 @@
         <v>6</v>
       </c>
       <c r="X259">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="Y259">
+        <v>4</v>
       </c>
     </row>
     <row r="260" spans="1:54" x14ac:dyDescent="0.3">
@@ -18889,10 +19051,10 @@
         <v>45539</v>
       </c>
       <c r="E261">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F261" s="2">
-        <v>0.98609999999999998</v>
+        <v>0.99080000000000001</v>
       </c>
       <c r="J261">
         <v>141</v>
@@ -18938,6 +19100,12 @@
       </c>
       <c r="X261">
         <v>2</v>
+      </c>
+      <c r="Y261">
+        <v>1</v>
+      </c>
+      <c r="Z261">
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:54" x14ac:dyDescent="0.3">
@@ -19004,10 +19172,10 @@
         <v>45602</v>
       </c>
       <c r="E263">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="F263" s="2">
-        <v>0.86809999999999998</v>
+        <v>0.90110000000000001</v>
       </c>
       <c r="I263">
         <v>2</v>
@@ -19052,6 +19220,9 @@
         <v>13</v>
       </c>
       <c r="W263">
+        <v>6</v>
+      </c>
+      <c r="X263">
         <v>1</v>
       </c>
     </row>
@@ -19069,10 +19240,10 @@
         <v>45652</v>
       </c>
       <c r="E264">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="F264" s="2">
-        <v>0.22989999999999999</v>
+        <v>0.4425</v>
       </c>
       <c r="J264">
         <v>3</v>
@@ -19099,7 +19270,10 @@
         <v>3</v>
       </c>
       <c r="V264">
-        <v>13</v>
+        <v>36</v>
+      </c>
+      <c r="W264">
+        <v>14</v>
       </c>
     </row>
     <row r="265" spans="1:54" x14ac:dyDescent="0.3">
@@ -19116,10 +19290,10 @@
         <v>45842</v>
       </c>
       <c r="E265">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="F265" s="2">
-        <v>0.93530000000000002</v>
+        <v>0.94030000000000002</v>
       </c>
       <c r="G265">
         <v>1</v>
@@ -19146,7 +19320,7 @@
         <v>25</v>
       </c>
       <c r="O265">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:54" x14ac:dyDescent="0.3">
@@ -19163,10 +19337,10 @@
         <v>45652</v>
       </c>
       <c r="E266">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="F266" s="2">
-        <v>0.58330000000000004</v>
+        <v>0.69910000000000005</v>
       </c>
       <c r="J266">
         <v>1</v>
@@ -19202,7 +19376,10 @@
         <v>4</v>
       </c>
       <c r="V266">
-        <v>10</v>
+        <v>27</v>
+      </c>
+      <c r="W266">
+        <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:54" x14ac:dyDescent="0.3">
@@ -19213,10 +19390,10 @@
         <v>139917</v>
       </c>
       <c r="E267" s="3">
-        <v>124473</v>
+        <v>125402</v>
       </c>
       <c r="F267" s="2">
-        <v>0.88959999999999995</v>
+        <v>0.89629999999999999</v>
       </c>
       <c r="G267" s="3">
         <v>1088</v>
@@ -19225,97 +19402,97 @@
         <v>12030</v>
       </c>
       <c r="I267" s="3">
-        <v>26298</v>
+        <v>26348</v>
       </c>
       <c r="J267" s="3">
-        <v>30675</v>
+        <v>30784</v>
       </c>
       <c r="K267" s="3">
-        <v>18200</v>
+        <v>18403</v>
       </c>
       <c r="L267" s="3">
-        <v>9887</v>
+        <v>10056</v>
       </c>
       <c r="M267" s="3">
-        <v>5718</v>
+        <v>5778</v>
       </c>
       <c r="N267" s="3">
-        <v>3793</v>
+        <v>3832</v>
       </c>
       <c r="O267" s="3">
-        <v>3240</v>
+        <v>3268</v>
       </c>
       <c r="P267" s="3">
-        <v>2775</v>
+        <v>2780</v>
       </c>
       <c r="Q267" s="3">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="R267" s="3">
-        <v>1203</v>
+        <v>1229</v>
       </c>
       <c r="S267" s="3">
-        <v>1293</v>
+        <v>1312</v>
       </c>
       <c r="T267" s="3">
-        <v>1399</v>
+        <v>1432</v>
       </c>
       <c r="U267">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="V267">
-        <v>544</v>
+        <v>590</v>
       </c>
       <c r="W267">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="X267">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="Y267">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Z267">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AA267">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="AB267">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="AC267">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AD267">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AE267">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF267">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AG267">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AH267">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI267">
         <v>138</v>
       </c>
       <c r="AJ267">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AK267">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AL267">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="AM267">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AN267">
         <v>55</v>
@@ -19327,22 +19504,22 @@
         <v>22</v>
       </c>
       <c r="AQ267">
+        <v>27</v>
+      </c>
+      <c r="AR267">
         <v>26</v>
       </c>
-      <c r="AR267">
-        <v>25</v>
-      </c>
       <c r="AS267">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AT267">
         <v>18</v>
       </c>
       <c r="AU267">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV267">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW267">
         <v>11</v>

--- a/입주율.xlsx
+++ b/입주율.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\입주율\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78E4C800-0CE3-460A-8775-E345AB497F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8EEAFC9-1D8A-46EA-9A28-0C549102DAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{31CB72D7-D90E-4BF3-AE86-941010CBC67F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{51E41DC2-83F2-4EED-BC8D-B2647803169E}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1959,13 +1959,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E7B31E3-7AB9-4198-B9E6-4B8AC4245050}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA550EEB-F9B0-4461-BE28-493423BF6289}">
   <dimension ref="A1:BB267"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="38.75" customWidth="1"/>
-    <col min="4" max="4" width="12.75" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -2774,10 +2770,10 @@
         <v>44935</v>
       </c>
       <c r="E12">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F12" s="2">
-        <v>0.97709999999999997</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I12">
         <v>27</v>
@@ -2859,6 +2855,9 @@
       </c>
       <c r="AN12">
         <v>2</v>
+      </c>
+      <c r="AU12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:54" x14ac:dyDescent="0.3">
@@ -3166,10 +3165,10 @@
         <v>44781</v>
       </c>
       <c r="E16">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F16" s="2">
-        <v>0.9647</v>
+        <v>0.96840000000000004</v>
       </c>
       <c r="H16">
         <v>10</v>
@@ -3223,7 +3222,7 @@
         <v>1</v>
       </c>
       <c r="AZ16">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:53" x14ac:dyDescent="0.3">
@@ -3825,10 +3824,10 @@
         <v>45930</v>
       </c>
       <c r="E26">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F26" s="2">
-        <v>0.58699999999999997</v>
+        <v>0.59630000000000005</v>
       </c>
       <c r="I26">
         <v>36</v>
@@ -3849,7 +3848,7 @@
         <v>25</v>
       </c>
       <c r="O26">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:53" x14ac:dyDescent="0.3">
@@ -3866,16 +3865,16 @@
         <v>46085</v>
       </c>
       <c r="E27">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="F27" s="2">
-        <v>0.18970000000000001</v>
+        <v>0.22839999999999999</v>
       </c>
       <c r="H27">
         <v>65</v>
       </c>
       <c r="I27">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:53" x14ac:dyDescent="0.3">
@@ -5801,10 +5800,10 @@
         <v>45694</v>
       </c>
       <c r="E57">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="F57" s="2">
-        <v>0.66910000000000003</v>
+        <v>0.67620000000000002</v>
       </c>
       <c r="L57">
         <v>53</v>
@@ -5837,7 +5836,7 @@
         <v>53</v>
       </c>
       <c r="V57">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:43" x14ac:dyDescent="0.3">
@@ -5990,10 +5989,10 @@
         <v>45498</v>
       </c>
       <c r="E60">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F60" s="2">
-        <v>0.89039999999999997</v>
+        <v>0.89170000000000005</v>
       </c>
       <c r="G60">
         <v>4</v>
@@ -6062,7 +6061,7 @@
         <v>10</v>
       </c>
       <c r="AC60">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:43" x14ac:dyDescent="0.3">
@@ -6079,10 +6078,10 @@
         <v>45762</v>
       </c>
       <c r="E61">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F61" s="2">
-        <v>0.78420000000000001</v>
+        <v>0.78910000000000002</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -6118,7 +6117,7 @@
         <v>23</v>
       </c>
       <c r="T61">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:43" x14ac:dyDescent="0.3">
@@ -6135,10 +6134,10 @@
         <v>45877</v>
       </c>
       <c r="E62">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F62" s="2">
-        <v>0.34100000000000003</v>
+        <v>0.34279999999999999</v>
       </c>
       <c r="I62">
         <v>54</v>
@@ -6162,7 +6161,7 @@
         <v>7</v>
       </c>
       <c r="P62">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:43" x14ac:dyDescent="0.3">
@@ -8205,10 +8204,10 @@
         <v>46006</v>
       </c>
       <c r="E92">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F92" s="2">
-        <v>9.0399999999999994E-2</v>
+        <v>9.4399999999999998E-2</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -8223,7 +8222,7 @@
         <v>26</v>
       </c>
       <c r="L92">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:51" x14ac:dyDescent="0.3">
@@ -8382,10 +8381,10 @@
         <v>45950</v>
       </c>
       <c r="E95">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="F95" s="2">
-        <v>0.41210000000000002</v>
+        <v>0.43290000000000001</v>
       </c>
       <c r="I95">
         <v>2</v>
@@ -8403,7 +8402,7 @@
         <v>37</v>
       </c>
       <c r="N95">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96" spans="1:51" x14ac:dyDescent="0.3">
@@ -8511,10 +8510,10 @@
         <v>45520</v>
       </c>
       <c r="E98">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F98" s="2">
-        <v>0.77139999999999997</v>
+        <v>0.77380000000000004</v>
       </c>
       <c r="G98">
         <v>8</v>
@@ -8571,6 +8570,9 @@
         <v>3</v>
       </c>
       <c r="Y98">
+        <v>1</v>
+      </c>
+      <c r="AB98">
         <v>1</v>
       </c>
     </row>
@@ -8588,10 +8590,10 @@
         <v>45602</v>
       </c>
       <c r="E99">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F99" s="2">
-        <v>0.81659999999999999</v>
+        <v>0.82530000000000003</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -8642,7 +8644,7 @@
         <v>5</v>
       </c>
       <c r="Y99">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:54" x14ac:dyDescent="0.3">
@@ -9763,10 +9765,10 @@
         <v>45415</v>
       </c>
       <c r="E115">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F115" s="2">
-        <v>0.90190000000000003</v>
+        <v>0.90410000000000001</v>
       </c>
       <c r="H115">
         <v>2</v>
@@ -9833,6 +9835,9 @@
       </c>
       <c r="AD115">
         <v>3</v>
+      </c>
+      <c r="AE115">
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:44" x14ac:dyDescent="0.3">
@@ -9982,16 +9987,16 @@
         <v>46007</v>
       </c>
       <c r="E118">
-        <v>588</v>
+        <v>784</v>
       </c>
       <c r="F118" s="2">
-        <v>0.29070000000000001</v>
+        <v>0.38750000000000001</v>
       </c>
       <c r="K118">
         <v>173</v>
       </c>
       <c r="L118">
-        <v>415</v>
+        <v>611</v>
       </c>
     </row>
     <row r="119" spans="1:44" x14ac:dyDescent="0.3">
@@ -10034,10 +10039,10 @@
         <v>45779</v>
       </c>
       <c r="E120">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F120" s="2">
-        <v>0.62929999999999997</v>
+        <v>0.63029999999999997</v>
       </c>
       <c r="H120">
         <v>178</v>
@@ -10073,7 +10078,7 @@
         <v>6</v>
       </c>
       <c r="S120">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:44" x14ac:dyDescent="0.3">
@@ -11168,10 +11173,10 @@
         <v>45152</v>
       </c>
       <c r="E138">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="F138" s="2">
-        <v>0.99819999999999998</v>
+        <v>0.99880000000000002</v>
       </c>
       <c r="I138">
         <v>611</v>
@@ -11240,6 +11245,9 @@
         <v>4</v>
       </c>
       <c r="AL138">
+        <v>1</v>
+      </c>
+      <c r="AN138">
         <v>1</v>
       </c>
     </row>
@@ -12302,10 +12310,10 @@
         <v>45630</v>
       </c>
       <c r="E153">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F153" s="2">
-        <v>0.97289999999999999</v>
+        <v>0.97670000000000001</v>
       </c>
       <c r="I153">
         <v>1</v>
@@ -12353,7 +12361,7 @@
         <v>7</v>
       </c>
       <c r="X153">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:48" x14ac:dyDescent="0.3">
@@ -12370,10 +12378,10 @@
         <v>45840</v>
       </c>
       <c r="E154">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F154" s="2">
-        <v>0.4511</v>
+        <v>0.4556</v>
       </c>
       <c r="J154">
         <v>11</v>
@@ -12397,7 +12405,7 @@
         <v>16</v>
       </c>
       <c r="Q154">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:48" x14ac:dyDescent="0.3">
@@ -12534,10 +12542,10 @@
         <v>45426</v>
       </c>
       <c r="E158">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F158" s="2">
-        <v>0.8952</v>
+        <v>0.89780000000000004</v>
       </c>
       <c r="H158">
         <v>51</v>
@@ -12595,6 +12603,9 @@
       </c>
       <c r="AD158">
         <v>3</v>
+      </c>
+      <c r="AE158">
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:48" x14ac:dyDescent="0.3">
@@ -12762,10 +12773,10 @@
         <v>45915</v>
       </c>
       <c r="E161">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F161" s="2">
-        <v>0.25</v>
+        <v>0.252</v>
       </c>
       <c r="K161">
         <v>2</v>
@@ -12780,7 +12791,7 @@
         <v>26</v>
       </c>
       <c r="O161">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:50" x14ac:dyDescent="0.3">
@@ -12882,10 +12893,10 @@
         <v>45569</v>
       </c>
       <c r="E164">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F164" s="2">
-        <v>0.45529999999999998</v>
+        <v>0.46339999999999998</v>
       </c>
       <c r="Q164">
         <v>1</v>
@@ -12915,7 +12926,7 @@
         <v>2</v>
       </c>
       <c r="Z164">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:50" x14ac:dyDescent="0.3">
@@ -13448,10 +13459,10 @@
         <v>45084</v>
       </c>
       <c r="E174">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F174" s="2">
-        <v>0.98870000000000002</v>
+        <v>0.99060000000000004</v>
       </c>
       <c r="H174">
         <v>62</v>
@@ -13511,6 +13522,9 @@
         <v>1</v>
       </c>
       <c r="AE174">
+        <v>1</v>
+      </c>
+      <c r="AP174">
         <v>1</v>
       </c>
     </row>
@@ -14977,10 +14991,10 @@
         <v>45974</v>
       </c>
       <c r="E196">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="F196" s="2">
-        <v>0.88109999999999999</v>
+        <v>0.88339999999999996</v>
       </c>
       <c r="I196">
         <v>711</v>
@@ -14995,7 +15009,7 @@
         <v>127</v>
       </c>
       <c r="M196">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="197" spans="1:49" x14ac:dyDescent="0.3">
@@ -15012,10 +15026,10 @@
         <v>45736</v>
       </c>
       <c r="E197">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F197" s="2">
-        <v>0.43869999999999998</v>
+        <v>0.44440000000000002</v>
       </c>
       <c r="K197">
         <v>6</v>
@@ -15048,7 +15062,7 @@
         <v>21</v>
       </c>
       <c r="U197">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:49" x14ac:dyDescent="0.3">
@@ -15065,10 +15079,10 @@
         <v>45987</v>
       </c>
       <c r="E198">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="F198" s="2">
-        <v>0.30409999999999998</v>
+        <v>0.31540000000000001</v>
       </c>
       <c r="J198">
         <v>18</v>
@@ -15080,7 +15094,7 @@
         <v>129</v>
       </c>
       <c r="M198">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="199" spans="1:49" x14ac:dyDescent="0.3">
@@ -16845,10 +16859,10 @@
         <v>45932</v>
       </c>
       <c r="E224">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F224" s="2">
-        <v>0.92169999999999996</v>
+        <v>0.93069999999999997</v>
       </c>
       <c r="H224">
         <v>53</v>
@@ -16869,7 +16883,7 @@
         <v>5</v>
       </c>
       <c r="N224">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:46" x14ac:dyDescent="0.3">
@@ -16886,10 +16900,10 @@
         <v>45932</v>
       </c>
       <c r="E225">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F225" s="2">
-        <v>0.93669999999999998</v>
+        <v>0.94940000000000002</v>
       </c>
       <c r="H225">
         <v>22</v>
@@ -16910,7 +16924,7 @@
         <v>4</v>
       </c>
       <c r="N225">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226" spans="1:46" x14ac:dyDescent="0.3">
@@ -16927,10 +16941,10 @@
         <v>45953</v>
       </c>
       <c r="E226">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F226" s="2">
-        <v>0.7823</v>
+        <v>0.78910000000000002</v>
       </c>
       <c r="I226">
         <v>1</v>
@@ -16948,7 +16962,7 @@
         <v>23</v>
       </c>
       <c r="N226">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227" spans="1:46" x14ac:dyDescent="0.3">
@@ -16965,16 +16979,16 @@
         <v>46084</v>
       </c>
       <c r="E227">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="F227" s="2">
-        <v>0.2802</v>
+        <v>0.36070000000000002</v>
       </c>
       <c r="H227">
         <v>39</v>
       </c>
       <c r="I227">
-        <v>128</v>
+        <v>176</v>
       </c>
     </row>
     <row r="228" spans="1:46" x14ac:dyDescent="0.3">
@@ -16991,10 +17005,10 @@
         <v>45993</v>
       </c>
       <c r="E228">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F228" s="2">
-        <v>0.58089999999999997</v>
+        <v>0.59419999999999995</v>
       </c>
       <c r="I228">
         <v>51</v>
@@ -17006,7 +17020,7 @@
         <v>49</v>
       </c>
       <c r="L228">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="229" spans="1:46" x14ac:dyDescent="0.3">
@@ -17097,10 +17111,10 @@
         <v>45909</v>
       </c>
       <c r="E230">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F230" s="2">
-        <v>0.43109999999999998</v>
+        <v>0.44130000000000003</v>
       </c>
       <c r="I230">
         <v>16</v>
@@ -17119,6 +17133,9 @@
       </c>
       <c r="N230">
         <v>14</v>
+      </c>
+      <c r="O230">
+        <v>4</v>
       </c>
     </row>
     <row r="231" spans="1:46" x14ac:dyDescent="0.3">
@@ -18905,10 +18922,10 @@
         <v>46031</v>
       </c>
       <c r="E255">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="F255" s="2">
-        <v>0.15640000000000001</v>
+        <v>0.1668</v>
       </c>
       <c r="I255">
         <v>50</v>
@@ -18917,7 +18934,7 @@
         <v>110</v>
       </c>
       <c r="K255">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="256" spans="1:53" x14ac:dyDescent="0.3">
@@ -19096,10 +19113,10 @@
         <v>45567</v>
       </c>
       <c r="E259">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F259" s="2">
-        <v>0.87890000000000001</v>
+        <v>0.88329999999999997</v>
       </c>
       <c r="I259">
         <v>6</v>
@@ -19153,7 +19170,7 @@
         <v>12</v>
       </c>
       <c r="Z259">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:54" x14ac:dyDescent="0.3">
@@ -19412,10 +19429,10 @@
         <v>45652</v>
       </c>
       <c r="E264">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F264" s="2">
-        <v>0.64370000000000005</v>
+        <v>0.67820000000000003</v>
       </c>
       <c r="J264">
         <v>3</v>
@@ -19448,7 +19465,7 @@
         <v>43</v>
       </c>
       <c r="X264">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="265" spans="1:54" x14ac:dyDescent="0.3">
@@ -19515,10 +19532,10 @@
         <v>45652</v>
       </c>
       <c r="E266">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F266" s="2">
-        <v>0.78239999999999998</v>
+        <v>0.79630000000000001</v>
       </c>
       <c r="J266">
         <v>1</v>
@@ -19560,7 +19577,7 @@
         <v>18</v>
       </c>
       <c r="X266">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="267" spans="1:54" x14ac:dyDescent="0.3">
@@ -19571,10 +19588,10 @@
         <v>139917</v>
       </c>
       <c r="E267" s="3">
-        <v>126947</v>
+        <v>127315</v>
       </c>
       <c r="F267" s="2">
-        <v>0.9073</v>
+        <v>0.90990000000000004</v>
       </c>
       <c r="G267" s="3">
         <v>1088</v>
@@ -19583,73 +19600,73 @@
         <v>12134</v>
       </c>
       <c r="I267" s="3">
-        <v>26514</v>
+        <v>26583</v>
       </c>
       <c r="J267" s="3">
         <v>30846</v>
       </c>
       <c r="K267" s="3">
-        <v>18630</v>
+        <v>18642</v>
       </c>
       <c r="L267" s="3">
-        <v>10633</v>
+        <v>10838</v>
       </c>
       <c r="M267" s="3">
-        <v>5855</v>
+        <v>5873</v>
       </c>
       <c r="N267" s="3">
-        <v>3890</v>
+        <v>3907</v>
       </c>
       <c r="O267" s="3">
-        <v>3275</v>
+        <v>3283</v>
       </c>
       <c r="P267" s="3">
-        <v>2803</v>
+        <v>2804</v>
       </c>
       <c r="Q267" s="3">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="R267" s="3">
         <v>1233</v>
       </c>
       <c r="S267" s="3">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="T267" s="3">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="U267">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="V267">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="W267">
         <v>580</v>
       </c>
       <c r="X267">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="Y267">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Z267">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AA267">
         <v>277</v>
       </c>
       <c r="AB267">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AC267">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AD267">
         <v>188</v>
       </c>
       <c r="AE267">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF267">
         <v>320</v>
@@ -19676,13 +19693,13 @@
         <v>43</v>
       </c>
       <c r="AN267">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AO267">
         <v>25</v>
       </c>
       <c r="AP267">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ267">
         <v>27</v>
@@ -19697,7 +19714,7 @@
         <v>18</v>
       </c>
       <c r="AU267">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV267">
         <v>21</v>
@@ -19712,7 +19729,7 @@
         <v>10</v>
       </c>
       <c r="AZ267">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA267">
         <v>6</v>

--- a/입주율.xlsx
+++ b/입주율.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\입주율\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFD405E2-C335-4F8F-9C35-4A3D0EACA89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A719E08E-5E6C-4D2A-A494-770E80393E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3876B0C-F26A-49C7-BAB2-888C174D272C}"/>
+    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{AEC2F4F2-95FC-4850-A0C8-E2044948BF70}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
   <si>
     <t>아파트코드</t>
   </si>
@@ -959,6 +959,9 @@
   </si>
   <si>
     <t>동인동센트럴대원칸타빌</t>
+  </si>
+  <si>
+    <t>태왕아너스 프리미어 아파트</t>
   </si>
   <si>
     <t>두류동 중흥s클래스셈텀포레</t>
@@ -1965,8 +1968,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{124312E5-A9E6-43BB-B849-67F92372A13D}">
-  <dimension ref="A1:BB269"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F06B7AC-1A61-4820-A882-6C02C38DC629}">
+  <dimension ref="A1:BB270"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.3">
@@ -2776,10 +2779,10 @@
         <v>44935</v>
       </c>
       <c r="E12">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F12" s="2">
-        <v>0.97799999999999998</v>
+        <v>0.97889999999999999</v>
       </c>
       <c r="I12">
         <v>27</v>
@@ -2863,6 +2866,9 @@
         <v>2</v>
       </c>
       <c r="AU12">
+        <v>1</v>
+      </c>
+      <c r="AV12">
         <v>1</v>
       </c>
     </row>
@@ -3777,10 +3783,10 @@
         <v>45841</v>
       </c>
       <c r="E25">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F25" s="2">
-        <v>0.97489999999999999</v>
+        <v>0.97660000000000002</v>
       </c>
       <c r="G25">
         <v>4</v>
@@ -3816,7 +3822,7 @@
         <v>2</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:53" x14ac:dyDescent="0.3">
@@ -3853,10 +3859,10 @@
         <v>45930</v>
       </c>
       <c r="E27">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="F27" s="2">
-        <v>0.61180000000000001</v>
+        <v>0.63660000000000005</v>
       </c>
       <c r="I27">
         <v>36</v>
@@ -3880,7 +3886,7 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:53" x14ac:dyDescent="0.3">
@@ -3897,10 +3903,10 @@
         <v>46085</v>
       </c>
       <c r="E28">
-        <v>242</v>
+        <v>319</v>
       </c>
       <c r="F28" s="2">
-        <v>0.44569999999999999</v>
+        <v>0.58750000000000002</v>
       </c>
       <c r="H28">
         <v>65</v>
@@ -3909,7 +3915,10 @@
         <v>116</v>
       </c>
       <c r="J28">
-        <v>61</v>
+        <v>120</v>
+      </c>
+      <c r="K28">
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:53" x14ac:dyDescent="0.3">
@@ -4189,10 +4198,10 @@
         <v>45370</v>
       </c>
       <c r="E33">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="F33" s="2">
-        <v>0.99790000000000001</v>
+        <v>0.99860000000000004</v>
       </c>
       <c r="G33">
         <v>9</v>
@@ -4243,6 +4252,9 @@
         <v>1</v>
       </c>
       <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="AH33">
         <v>1</v>
       </c>
     </row>
@@ -5841,10 +5853,10 @@
         <v>45694</v>
       </c>
       <c r="E58">
-        <v>610</v>
+        <v>650</v>
       </c>
       <c r="F58" s="2">
-        <v>0.7288</v>
+        <v>0.77659999999999996</v>
       </c>
       <c r="L58">
         <v>53</v>
@@ -5880,7 +5892,10 @@
         <v>37</v>
       </c>
       <c r="W58">
-        <v>24</v>
+        <v>47</v>
+      </c>
+      <c r="X58">
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:43" x14ac:dyDescent="0.3">
@@ -5968,10 +5983,10 @@
         <v>45608</v>
       </c>
       <c r="E60">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F60" s="2">
-        <v>0.92759999999999998</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="H60">
         <v>2</v>
@@ -6017,6 +6032,9 @@
       </c>
       <c r="X60">
         <v>1</v>
+      </c>
+      <c r="AA60">
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:43" x14ac:dyDescent="0.3">
@@ -6033,10 +6051,10 @@
         <v>45498</v>
       </c>
       <c r="E61">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="F61" s="2">
-        <v>0.90300000000000002</v>
+        <v>0.91439999999999999</v>
       </c>
       <c r="G61">
         <v>4</v>
@@ -6108,7 +6126,10 @@
         <v>7</v>
       </c>
       <c r="AD61">
-        <v>4</v>
+        <v>10</v>
+      </c>
+      <c r="AE61">
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:43" x14ac:dyDescent="0.3">
@@ -6125,10 +6146,10 @@
         <v>45762</v>
       </c>
       <c r="E62">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="F62" s="2">
-        <v>0.82040000000000002</v>
+        <v>0.85340000000000005</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -6167,6 +6188,9 @@
         <v>24</v>
       </c>
       <c r="U62">
+        <v>20</v>
+      </c>
+      <c r="V62">
         <v>8</v>
       </c>
     </row>
@@ -6184,10 +6208,10 @@
         <v>45877</v>
       </c>
       <c r="E63">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="F63" s="2">
-        <v>0.35510000000000003</v>
+        <v>0.36749999999999999</v>
       </c>
       <c r="I63">
         <v>54</v>
@@ -6214,7 +6238,10 @@
         <v>9</v>
       </c>
       <c r="Q63">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="R63">
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:43" x14ac:dyDescent="0.3">
@@ -6568,10 +6595,10 @@
         <v>45271</v>
       </c>
       <c r="E69">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F69" s="2">
-        <v>0.99870000000000003</v>
+        <v>1</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6620,6 +6647,9 @@
       </c>
       <c r="AE69">
         <v>2</v>
+      </c>
+      <c r="AK69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:50" x14ac:dyDescent="0.3">
@@ -7100,10 +7130,10 @@
         <v>45183</v>
       </c>
       <c r="E77">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F77" s="2">
-        <v>0.9637</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="H77">
         <v>5</v>
@@ -7169,7 +7199,7 @@
         <v>2</v>
       </c>
       <c r="AN77">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:50" x14ac:dyDescent="0.3">
@@ -7384,10 +7414,10 @@
         <v>44985</v>
       </c>
       <c r="E81">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F81" s="2">
-        <v>0.96970000000000001</v>
+        <v>0.97289999999999999</v>
       </c>
       <c r="H81">
         <v>43</v>
@@ -7471,7 +7501,7 @@
         <v>2</v>
       </c>
       <c r="AU81">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:51" x14ac:dyDescent="0.3">
@@ -8012,10 +8042,10 @@
         <v>45253</v>
       </c>
       <c r="E89">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F89" s="2">
-        <v>0.35420000000000001</v>
+        <v>0.36459999999999998</v>
       </c>
       <c r="K89">
         <v>1</v>
@@ -8072,6 +8102,9 @@
         <v>2</v>
       </c>
       <c r="AH89">
+        <v>1</v>
+      </c>
+      <c r="AL89">
         <v>1</v>
       </c>
     </row>
@@ -8204,10 +8237,10 @@
         <v>45560</v>
       </c>
       <c r="E92">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F92" s="2">
-        <v>0.99570000000000003</v>
+        <v>0.99680000000000002</v>
       </c>
       <c r="H92">
         <v>18</v>
@@ -8261,7 +8294,7 @@
         <v>1</v>
       </c>
       <c r="AB92">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:51" x14ac:dyDescent="0.3">
@@ -8278,10 +8311,16 @@
         <v>46148</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F93" s="2">
-        <v>0</v>
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="H93">
+        <v>10</v>
+      </c>
+      <c r="I93">
+        <v>46</v>
       </c>
     </row>
     <row r="94" spans="1:51" x14ac:dyDescent="0.3">
@@ -8298,10 +8337,10 @@
         <v>46006</v>
       </c>
       <c r="E94">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="F94" s="2">
-        <v>0.1263</v>
+        <v>0.15559999999999999</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -8319,7 +8358,10 @@
         <v>14</v>
       </c>
       <c r="M94">
-        <v>14</v>
+        <v>32</v>
+      </c>
+      <c r="N94">
+        <v>4</v>
       </c>
     </row>
     <row r="95" spans="1:51" x14ac:dyDescent="0.3">
@@ -8478,10 +8520,10 @@
         <v>45950</v>
       </c>
       <c r="E97">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F97" s="2">
-        <v>0.5161</v>
+        <v>0.5444</v>
       </c>
       <c r="I97">
         <v>2</v>
@@ -8502,7 +8544,10 @@
         <v>47</v>
       </c>
       <c r="O97">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="P97">
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:53" x14ac:dyDescent="0.3">
@@ -8696,10 +8741,10 @@
         <v>45602</v>
       </c>
       <c r="E101">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F101" s="2">
-        <v>0.85150000000000003</v>
+        <v>0.86460000000000004</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -8753,6 +8798,9 @@
         <v>10</v>
       </c>
       <c r="Z101">
+        <v>3</v>
+      </c>
+      <c r="AA101">
         <v>1</v>
       </c>
     </row>
@@ -8770,10 +8818,10 @@
         <v>45623</v>
       </c>
       <c r="E102">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F102" s="2">
-        <v>0.95830000000000004</v>
+        <v>0.96009999999999995</v>
       </c>
       <c r="I102">
         <v>7</v>
@@ -8818,7 +8866,7 @@
         <v>2</v>
       </c>
       <c r="Z102">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:53" x14ac:dyDescent="0.3">
@@ -10037,10 +10085,10 @@
         <v>45614</v>
       </c>
       <c r="E119">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F119" s="2">
-        <v>0.99719999999999998</v>
+        <v>0.99819999999999998</v>
       </c>
       <c r="G119">
         <v>4</v>
@@ -10091,6 +10139,9 @@
         <v>1</v>
       </c>
       <c r="Z119">
+        <v>1</v>
+      </c>
+      <c r="AA119">
         <v>1</v>
       </c>
     </row>
@@ -10108,10 +10159,10 @@
         <v>46007</v>
       </c>
       <c r="E120">
-        <v>1317</v>
+        <v>1636</v>
       </c>
       <c r="F120" s="2">
-        <v>0.65100000000000002</v>
+        <v>0.80869999999999997</v>
       </c>
       <c r="K120">
         <v>173</v>
@@ -10120,7 +10171,10 @@
         <v>944</v>
       </c>
       <c r="M120">
-        <v>200</v>
+        <v>414</v>
+      </c>
+      <c r="N120">
+        <v>105</v>
       </c>
     </row>
     <row r="121" spans="1:54" x14ac:dyDescent="0.3">
@@ -10137,10 +10191,10 @@
         <v>46000</v>
       </c>
       <c r="E121">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F121" s="2">
-        <v>6.2300000000000001E-2</v>
+        <v>0.10730000000000001</v>
       </c>
       <c r="K121">
         <v>4</v>
@@ -10149,7 +10203,10 @@
         <v>10</v>
       </c>
       <c r="M121">
-        <v>4</v>
+        <v>15</v>
+      </c>
+      <c r="N121">
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:54" x14ac:dyDescent="0.3">
@@ -10166,10 +10223,10 @@
         <v>45779</v>
       </c>
       <c r="E122">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="F122" s="2">
-        <v>0.63919999999999999</v>
+        <v>0.6482</v>
       </c>
       <c r="H122">
         <v>178</v>
@@ -10208,6 +10265,9 @@
         <v>10</v>
       </c>
       <c r="T122">
+        <v>9</v>
+      </c>
+      <c r="U122">
         <v>5</v>
       </c>
     </row>
@@ -10254,10 +10314,10 @@
         <v>45636</v>
       </c>
       <c r="E124">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F124" s="2">
-        <v>0.92600000000000005</v>
+        <v>0.93149999999999999</v>
       </c>
       <c r="H124">
         <v>3</v>
@@ -10305,6 +10365,12 @@
         <v>1</v>
       </c>
       <c r="W124">
+        <v>1</v>
+      </c>
+      <c r="Y124">
+        <v>1</v>
+      </c>
+      <c r="Z124">
         <v>1</v>
       </c>
     </row>
@@ -10881,10 +10947,10 @@
         <v>44903</v>
       </c>
       <c r="E133">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F133" s="2">
-        <v>0.98870000000000002</v>
+        <v>0.99250000000000005</v>
       </c>
       <c r="J133">
         <v>46</v>
@@ -10941,6 +11007,9 @@
         <v>2</v>
       </c>
       <c r="AS133">
+        <v>1</v>
+      </c>
+      <c r="AW133">
         <v>1</v>
       </c>
     </row>
@@ -11605,10 +11674,10 @@
         <v>45317</v>
       </c>
       <c r="E144">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F144" s="2">
-        <v>0.58640000000000003</v>
+        <v>0.59160000000000001</v>
       </c>
       <c r="I144">
         <v>17</v>
@@ -11668,6 +11737,9 @@
         <v>1</v>
       </c>
       <c r="AI144">
+        <v>1</v>
+      </c>
+      <c r="AJ144">
         <v>1</v>
       </c>
     </row>
@@ -12328,10 +12400,10 @@
         <v>45343</v>
       </c>
       <c r="E153">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F153" s="2">
-        <v>0.99350000000000005</v>
+        <v>0.99509999999999998</v>
       </c>
       <c r="I153">
         <v>126</v>
@@ -12401,6 +12473,9 @@
       </c>
       <c r="AG153">
         <v>3</v>
+      </c>
+      <c r="AI153">
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:51" x14ac:dyDescent="0.3">
@@ -12446,10 +12521,10 @@
         <v>45630</v>
       </c>
       <c r="E155">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F155" s="2">
-        <v>0.97670000000000001</v>
+        <v>0.98060000000000003</v>
       </c>
       <c r="I155">
         <v>1</v>
@@ -12498,6 +12573,9 @@
       </c>
       <c r="X155">
         <v>2</v>
+      </c>
+      <c r="Y155">
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:51" x14ac:dyDescent="0.3">
@@ -12514,10 +12592,10 @@
         <v>45840</v>
       </c>
       <c r="E156">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="F156" s="2">
-        <v>0.51329999999999998</v>
+        <v>0.55330000000000001</v>
       </c>
       <c r="J156">
         <v>11</v>
@@ -12544,7 +12622,10 @@
         <v>15</v>
       </c>
       <c r="R156">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="S156">
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:51" x14ac:dyDescent="0.3">
@@ -12684,10 +12765,10 @@
         <v>45426</v>
       </c>
       <c r="E160">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F160" s="2">
-        <v>0.9032</v>
+        <v>0.90859999999999996</v>
       </c>
       <c r="H160">
         <v>51</v>
@@ -12748,6 +12829,9 @@
       </c>
       <c r="AE160">
         <v>3</v>
+      </c>
+      <c r="AG160">
+        <v>2</v>
       </c>
     </row>
     <row r="161" spans="1:50" x14ac:dyDescent="0.3">
@@ -12835,10 +12919,10 @@
         <v>45502</v>
       </c>
       <c r="E162">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F162" s="2">
-        <v>0.99329999999999996</v>
+        <v>0.99560000000000004</v>
       </c>
       <c r="H162">
         <v>99</v>
@@ -12898,6 +12982,9 @@
         <v>1</v>
       </c>
       <c r="AB162">
+        <v>1</v>
+      </c>
+      <c r="AE162">
         <v>1</v>
       </c>
     </row>
@@ -12915,10 +13002,10 @@
         <v>45915</v>
       </c>
       <c r="E163">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F163" s="2">
-        <v>0.27239999999999998</v>
+        <v>0.28660000000000002</v>
       </c>
       <c r="K163">
         <v>2</v>
@@ -12936,7 +13023,10 @@
         <v>10</v>
       </c>
       <c r="P163">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="Q163">
+        <v>4</v>
       </c>
     </row>
     <row r="164" spans="1:50" x14ac:dyDescent="0.3">
@@ -13038,10 +13128,10 @@
         <v>45569</v>
       </c>
       <c r="E166">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F166" s="2">
-        <v>0.49590000000000001</v>
+        <v>0.52849999999999997</v>
       </c>
       <c r="Q166">
         <v>1</v>
@@ -13074,6 +13164,9 @@
         <v>5</v>
       </c>
       <c r="AA166">
+        <v>4</v>
+      </c>
+      <c r="AB166">
         <v>2</v>
       </c>
     </row>
@@ -13289,13 +13382,16 @@
         <v>45366</v>
       </c>
       <c r="E170">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F170" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="O170">
         <v>4</v>
+      </c>
+      <c r="AI170">
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:50" x14ac:dyDescent="0.3">
@@ -14932,10 +15028,10 @@
         <v>45397</v>
       </c>
       <c r="E195">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F195" s="2">
-        <v>0.94430000000000003</v>
+        <v>0.94520000000000004</v>
       </c>
       <c r="G195">
         <v>22</v>
@@ -14989,6 +15085,9 @@
         <v>1</v>
       </c>
       <c r="AA195">
+        <v>1</v>
+      </c>
+      <c r="AH195">
         <v>1</v>
       </c>
     </row>
@@ -15151,10 +15250,10 @@
         <v>45974</v>
       </c>
       <c r="E198">
-        <v>1588</v>
+        <v>1607</v>
       </c>
       <c r="F198" s="2">
-        <v>0.90329999999999999</v>
+        <v>0.91410000000000002</v>
       </c>
       <c r="I198">
         <v>711</v>
@@ -15172,7 +15271,10 @@
         <v>36</v>
       </c>
       <c r="N198">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="O198">
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:49" x14ac:dyDescent="0.3">
@@ -15189,10 +15291,10 @@
         <v>45736</v>
       </c>
       <c r="E199">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="F199" s="2">
-        <v>0.4672</v>
+        <v>0.51</v>
       </c>
       <c r="K199">
         <v>6</v>
@@ -15228,7 +15330,10 @@
         <v>11</v>
       </c>
       <c r="V199">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="W199">
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:49" x14ac:dyDescent="0.3">
@@ -15245,10 +15350,10 @@
         <v>45987</v>
       </c>
       <c r="E200">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="F200" s="2">
-        <v>0.34189999999999998</v>
+        <v>0.35799999999999998</v>
       </c>
       <c r="J200">
         <v>18</v>
@@ -15263,7 +15368,10 @@
         <v>53</v>
       </c>
       <c r="N200">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="O200">
+        <v>6</v>
       </c>
     </row>
     <row r="201" spans="1:49" x14ac:dyDescent="0.3">
@@ -15532,10 +15640,10 @@
         <v>45295</v>
       </c>
       <c r="E204">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F204" s="2">
-        <v>0.99419999999999997</v>
+        <v>0.99619999999999997</v>
       </c>
       <c r="I204">
         <v>15</v>
@@ -15571,6 +15679,9 @@
         <v>1</v>
       </c>
       <c r="AG204">
+        <v>1</v>
+      </c>
+      <c r="AJ204">
         <v>1</v>
       </c>
     </row>
@@ -15804,10 +15915,10 @@
         <v>45112</v>
       </c>
       <c r="E208">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F208" s="2">
-        <v>0.98740000000000006</v>
+        <v>0.99370000000000003</v>
       </c>
       <c r="H208">
         <v>7</v>
@@ -15859,6 +15970,9 @@
       </c>
       <c r="AO208">
         <v>2</v>
+      </c>
+      <c r="AP208">
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:52" x14ac:dyDescent="0.3">
@@ -16040,10 +16154,10 @@
         <v>45226</v>
       </c>
       <c r="E212">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F212" s="2">
-        <v>0.45879999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G212">
         <v>1</v>
@@ -16136,7 +16250,10 @@
         <v>1</v>
       </c>
       <c r="AM212">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="AN212">
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:52" x14ac:dyDescent="0.3">
@@ -16153,10 +16270,10 @@
         <v>45226</v>
       </c>
       <c r="E213">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F213" s="2">
-        <v>0.99199999999999999</v>
+        <v>0.99460000000000004</v>
       </c>
       <c r="H213">
         <v>56</v>
@@ -16226,6 +16343,9 @@
       </c>
       <c r="AG213">
         <v>11</v>
+      </c>
+      <c r="AN213">
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:52" x14ac:dyDescent="0.3">
@@ -17040,10 +17160,10 @@
         <v>45932</v>
       </c>
       <c r="E226">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F226" s="2">
-        <v>0.94279999999999997</v>
+        <v>0.94579999999999997</v>
       </c>
       <c r="H226">
         <v>53</v>
@@ -17067,7 +17187,7 @@
         <v>8</v>
       </c>
       <c r="O226">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227" spans="1:46" x14ac:dyDescent="0.3">
@@ -17084,10 +17204,10 @@
         <v>45932</v>
       </c>
       <c r="E227">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F227" s="2">
-        <v>0.96199999999999997</v>
+        <v>0.96840000000000004</v>
       </c>
       <c r="H227">
         <v>22</v>
@@ -17111,7 +17231,7 @@
         <v>3</v>
       </c>
       <c r="O227">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:46" x14ac:dyDescent="0.3">
@@ -17128,10 +17248,10 @@
         <v>45953</v>
       </c>
       <c r="E228">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F228" s="2">
-        <v>0.88439999999999996</v>
+        <v>0.91839999999999999</v>
       </c>
       <c r="I228">
         <v>1</v>
@@ -17152,7 +17272,7 @@
         <v>21</v>
       </c>
       <c r="O228">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="229" spans="1:46" x14ac:dyDescent="0.3">
@@ -17169,10 +17289,10 @@
         <v>46084</v>
       </c>
       <c r="E229">
-        <v>333</v>
+        <v>432</v>
       </c>
       <c r="F229" s="2">
-        <v>0.55869999999999997</v>
+        <v>0.7248</v>
       </c>
       <c r="H229">
         <v>39</v>
@@ -17181,7 +17301,10 @@
         <v>233</v>
       </c>
       <c r="J229">
-        <v>61</v>
+        <v>141</v>
+      </c>
+      <c r="K229">
+        <v>19</v>
       </c>
     </row>
     <row r="230" spans="1:46" x14ac:dyDescent="0.3">
@@ -17198,10 +17321,10 @@
         <v>45993</v>
       </c>
       <c r="E230">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="F230" s="2">
-        <v>0.64749999999999996</v>
+        <v>0.69840000000000002</v>
       </c>
       <c r="I230">
         <v>51</v>
@@ -17216,7 +17339,10 @@
         <v>34</v>
       </c>
       <c r="M230">
-        <v>10</v>
+        <v>28</v>
+      </c>
+      <c r="N230">
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:46" x14ac:dyDescent="0.3">
@@ -17307,10 +17433,10 @@
         <v>45909</v>
       </c>
       <c r="E232">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F232" s="2">
-        <v>0.4617</v>
+        <v>0.47699999999999998</v>
       </c>
       <c r="I232">
         <v>16</v>
@@ -17334,7 +17460,10 @@
         <v>7</v>
       </c>
       <c r="P232">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="Q232">
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:46" x14ac:dyDescent="0.3">
@@ -17351,10 +17480,10 @@
         <v>45443</v>
       </c>
       <c r="E233">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F233" s="2">
-        <v>0.99729999999999996</v>
+        <v>1</v>
       </c>
       <c r="I233">
         <v>10</v>
@@ -17400,6 +17529,9 @@
       </c>
       <c r="W233">
         <v>2</v>
+      </c>
+      <c r="AF233">
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:46" x14ac:dyDescent="0.3">
@@ -18282,10 +18414,10 @@
         <v>44978</v>
       </c>
       <c r="E244">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F244" s="2">
-        <v>0.98750000000000004</v>
+        <v>0.99380000000000002</v>
       </c>
       <c r="J244">
         <v>36</v>
@@ -18360,6 +18492,9 @@
         <v>1</v>
       </c>
       <c r="AU244">
+        <v>2</v>
+      </c>
+      <c r="AV244">
         <v>1</v>
       </c>
     </row>
@@ -18989,10 +19124,10 @@
         <v>45343</v>
       </c>
       <c r="E254">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F254" s="2">
-        <v>0.99470000000000003</v>
+        <v>0.99650000000000005</v>
       </c>
       <c r="H254">
         <v>1</v>
@@ -19068,6 +19203,9 @@
       </c>
       <c r="AG254">
         <v>4</v>
+      </c>
+      <c r="AI254">
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:53" x14ac:dyDescent="0.3">
@@ -19130,10 +19268,10 @@
         <v>46031</v>
       </c>
       <c r="E257">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="F257" s="2">
-        <v>0.2092</v>
+        <v>0.22389999999999999</v>
       </c>
       <c r="I257">
         <v>50</v>
@@ -19145,7 +19283,10 @@
         <v>60</v>
       </c>
       <c r="L257">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="M257">
+        <v>10</v>
       </c>
     </row>
     <row r="258" spans="1:54" x14ac:dyDescent="0.3">
@@ -19185,10 +19326,10 @@
         <v>45860</v>
       </c>
       <c r="E259">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="F259" s="2">
-        <v>0.97189999999999999</v>
+        <v>0.97409999999999997</v>
       </c>
       <c r="G259">
         <v>2</v>
@@ -19224,7 +19365,7 @@
         <v>2</v>
       </c>
       <c r="R259">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="260" spans="1:54" x14ac:dyDescent="0.3">
@@ -19241,10 +19382,10 @@
         <v>45446</v>
       </c>
       <c r="E260">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F260" s="2">
-        <v>0.97799999999999998</v>
+        <v>0.98019999999999996</v>
       </c>
       <c r="G260">
         <v>1</v>
@@ -19315,664 +19456,699 @@
       <c r="AE260">
         <v>2</v>
       </c>
+      <c r="AF260">
+        <v>1</v>
+      </c>
     </row>
     <row r="261" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A261">
-        <v>201433</v>
+        <v>201500</v>
       </c>
       <c r="B261" t="s">
         <v>313</v>
       </c>
       <c r="C261">
-        <v>454</v>
+        <v>200</v>
       </c>
       <c r="D261" s="1">
-        <v>45567</v>
+        <v>46177</v>
       </c>
       <c r="E261">
-        <v>414</v>
+        <v>10</v>
       </c>
       <c r="F261" s="2">
-        <v>0.91190000000000004</v>
-      </c>
-      <c r="I261">
-        <v>6</v>
-      </c>
-      <c r="J261">
-        <v>134</v>
-      </c>
-      <c r="K261">
-        <v>96</v>
-      </c>
-      <c r="L261">
-        <v>49</v>
-      </c>
-      <c r="M261">
-        <v>40</v>
-      </c>
-      <c r="N261">
-        <v>11</v>
-      </c>
-      <c r="O261">
-        <v>9</v>
-      </c>
-      <c r="P261">
-        <v>5</v>
-      </c>
-      <c r="Q261">
-        <v>2</v>
-      </c>
-      <c r="R261">
-        <v>2</v>
-      </c>
-      <c r="S261">
-        <v>2</v>
-      </c>
-      <c r="T261">
-        <v>1</v>
-      </c>
-      <c r="U261">
+        <v>0.05</v>
+      </c>
+      <c r="G261">
         <v>8</v>
       </c>
-      <c r="V261">
-        <v>5</v>
-      </c>
-      <c r="W261">
-        <v>6</v>
-      </c>
-      <c r="X261">
-        <v>8</v>
-      </c>
-      <c r="Y261">
-        <v>12</v>
-      </c>
-      <c r="Z261">
-        <v>10</v>
-      </c>
-      <c r="AA261">
-        <v>8</v>
+      <c r="H261">
+        <v>2</v>
       </c>
     </row>
     <row r="262" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A262">
-        <v>201418</v>
+        <v>201433</v>
       </c>
       <c r="B262" t="s">
         <v>314</v>
       </c>
       <c r="C262">
-        <v>335</v>
+        <v>454</v>
       </c>
       <c r="D262" s="1">
-        <v>45525</v>
+        <v>45567</v>
       </c>
       <c r="E262">
-        <v>335</v>
+        <v>421</v>
       </c>
       <c r="F262" s="2">
-        <v>1</v>
-      </c>
-      <c r="H262">
-        <v>1</v>
+        <v>0.92730000000000001</v>
       </c>
       <c r="I262">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="J262">
-        <v>197</v>
+        <v>134</v>
       </c>
       <c r="K262">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="L262">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="M262">
+        <v>40</v>
+      </c>
+      <c r="N262">
+        <v>11</v>
+      </c>
+      <c r="O262">
+        <v>9</v>
+      </c>
+      <c r="P262">
+        <v>5</v>
+      </c>
+      <c r="Q262">
+        <v>2</v>
+      </c>
+      <c r="R262">
+        <v>2</v>
+      </c>
+      <c r="S262">
+        <v>2</v>
+      </c>
+      <c r="T262">
+        <v>1</v>
+      </c>
+      <c r="U262">
         <v>8</v>
       </c>
-      <c r="N262">
-        <v>4</v>
-      </c>
-      <c r="O262">
-        <v>1</v>
-      </c>
-      <c r="P262">
-        <v>2</v>
-      </c>
-      <c r="Q262">
-        <v>1</v>
+      <c r="V262">
+        <v>5</v>
       </c>
       <c r="W262">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="X262">
+        <v>8</v>
+      </c>
+      <c r="Y262">
+        <v>12</v>
+      </c>
+      <c r="Z262">
+        <v>10</v>
+      </c>
+      <c r="AA262">
+        <v>14</v>
+      </c>
+      <c r="AB262">
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A263">
-        <v>201454</v>
+        <v>201418</v>
       </c>
       <c r="B263" t="s">
         <v>315</v>
       </c>
       <c r="C263">
-        <v>433</v>
+        <v>335</v>
       </c>
       <c r="D263" s="1">
-        <v>45539</v>
+        <v>45525</v>
       </c>
       <c r="E263">
-        <v>430</v>
+        <v>335</v>
       </c>
       <c r="F263" s="2">
-        <v>0.99309999999999998</v>
+        <v>1</v>
+      </c>
+      <c r="H263">
+        <v>1</v>
+      </c>
+      <c r="I263">
+        <v>92</v>
       </c>
       <c r="J263">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="K263">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="L263">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="M263">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="N263">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="O263">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="P263">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="Q263">
-        <v>19</v>
-      </c>
-      <c r="R263">
-        <v>11</v>
-      </c>
-      <c r="S263">
-        <v>5</v>
-      </c>
-      <c r="T263">
-        <v>11</v>
-      </c>
-      <c r="U263">
-        <v>9</v>
-      </c>
-      <c r="V263">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W263">
-        <v>2</v>
-      </c>
-      <c r="X263">
-        <v>2</v>
-      </c>
-      <c r="Y263">
-        <v>1</v>
-      </c>
-      <c r="Z263">
         <v>2</v>
       </c>
     </row>
     <row r="264" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A264">
-        <v>201480</v>
+        <v>201454</v>
       </c>
       <c r="B264" t="s">
         <v>316</v>
       </c>
       <c r="C264">
-        <v>117</v>
+        <v>433</v>
       </c>
       <c r="D264" s="1">
-        <v>45762</v>
+        <v>45539</v>
       </c>
       <c r="E264">
-        <v>109</v>
+        <v>430</v>
       </c>
       <c r="F264" s="2">
-        <v>0.93159999999999998</v>
-      </c>
-      <c r="H264">
-        <v>10</v>
-      </c>
-      <c r="I264">
-        <v>34</v>
+        <v>0.99309999999999998</v>
       </c>
       <c r="J264">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="K264">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="L264">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="M264">
+        <v>30</v>
+      </c>
+      <c r="N264">
+        <v>22</v>
+      </c>
+      <c r="O264">
+        <v>16</v>
+      </c>
+      <c r="P264">
+        <v>28</v>
+      </c>
+      <c r="Q264">
+        <v>19</v>
+      </c>
+      <c r="R264">
+        <v>11</v>
+      </c>
+      <c r="S264">
+        <v>5</v>
+      </c>
+      <c r="T264">
+        <v>11</v>
+      </c>
+      <c r="U264">
         <v>9</v>
       </c>
-      <c r="N264">
-        <v>5</v>
-      </c>
-      <c r="O264">
-        <v>2</v>
-      </c>
-      <c r="P264">
-        <v>1</v>
-      </c>
-      <c r="Q264">
-        <v>1</v>
-      </c>
-      <c r="T264">
+      <c r="V264">
+        <v>12</v>
+      </c>
+      <c r="W264">
+        <v>2</v>
+      </c>
+      <c r="X264">
+        <v>2</v>
+      </c>
+      <c r="Y264">
+        <v>1</v>
+      </c>
+      <c r="Z264">
         <v>2</v>
       </c>
     </row>
     <row r="265" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A265">
-        <v>201465</v>
+        <v>201480</v>
       </c>
       <c r="B265" t="s">
         <v>317</v>
       </c>
       <c r="C265">
-        <v>182</v>
+        <v>117</v>
       </c>
       <c r="D265" s="1">
-        <v>45602</v>
+        <v>45762</v>
       </c>
       <c r="E265">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="F265" s="2">
-        <v>0.92310000000000003</v>
+        <v>0.93159999999999998</v>
+      </c>
+      <c r="H265">
+        <v>10</v>
       </c>
       <c r="I265">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="J265">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K265">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L265">
+        <v>10</v>
+      </c>
+      <c r="M265">
         <v>9</v>
       </c>
-      <c r="M265">
-        <v>8</v>
-      </c>
       <c r="N265">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O265">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="P265">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q265">
-        <v>12</v>
-      </c>
-      <c r="R265">
-        <v>14</v>
-      </c>
-      <c r="S265">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T265">
-        <v>14</v>
-      </c>
-      <c r="U265">
-        <v>13</v>
-      </c>
-      <c r="V265">
-        <v>13</v>
-      </c>
-      <c r="W265">
-        <v>6</v>
-      </c>
-      <c r="X265">
-        <v>3</v>
-      </c>
-      <c r="Y265">
         <v>2</v>
       </c>
     </row>
     <row r="266" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A266">
-        <v>201471</v>
+        <v>201465</v>
       </c>
       <c r="B266" t="s">
         <v>318</v>
       </c>
       <c r="C266">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D266" s="1">
-        <v>45652</v>
+        <v>45602</v>
       </c>
       <c r="E266">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="F266" s="2">
-        <v>0.75290000000000001</v>
+        <v>0.92310000000000003</v>
+      </c>
+      <c r="I266">
+        <v>2</v>
       </c>
       <c r="J266">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K266">
+        <v>13</v>
+      </c>
+      <c r="L266">
+        <v>9</v>
+      </c>
+      <c r="M266">
+        <v>8</v>
+      </c>
+      <c r="N266">
+        <v>13</v>
+      </c>
+      <c r="O266">
+        <v>13</v>
+      </c>
+      <c r="P266">
+        <v>9</v>
+      </c>
+      <c r="Q266">
+        <v>12</v>
+      </c>
+      <c r="R266">
+        <v>14</v>
+      </c>
+      <c r="S266">
+        <v>11</v>
+      </c>
+      <c r="T266">
+        <v>14</v>
+      </c>
+      <c r="U266">
+        <v>13</v>
+      </c>
+      <c r="V266">
+        <v>13</v>
+      </c>
+      <c r="W266">
         <v>6</v>
       </c>
-      <c r="L266">
-        <v>5</v>
-      </c>
-      <c r="M266">
-        <v>5</v>
-      </c>
-      <c r="N266">
-        <v>3</v>
-      </c>
-      <c r="O266">
-        <v>1</v>
-      </c>
-      <c r="T266">
-        <v>1</v>
-      </c>
-      <c r="U266">
-        <v>3</v>
-      </c>
-      <c r="V266">
-        <v>36</v>
-      </c>
-      <c r="W266">
-        <v>43</v>
-      </c>
       <c r="X266">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="Y266">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A267">
-        <v>201453</v>
+        <v>201471</v>
       </c>
       <c r="B267" t="s">
         <v>319</v>
       </c>
-      <c r="C267" s="3">
-        <v>1005</v>
+      <c r="C267">
+        <v>174</v>
       </c>
       <c r="D267" s="1">
-        <v>45842</v>
+        <v>45652</v>
       </c>
       <c r="E267">
-        <v>954</v>
+        <v>143</v>
       </c>
       <c r="F267" s="2">
-        <v>0.94930000000000003</v>
-      </c>
-      <c r="G267">
-        <v>1</v>
-      </c>
-      <c r="H267">
-        <v>264</v>
-      </c>
-      <c r="I267">
-        <v>326</v>
+        <v>0.82179999999999997</v>
       </c>
       <c r="J267">
-        <v>165</v>
+        <v>3</v>
       </c>
       <c r="K267">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="L267">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="M267">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="N267">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="O267">
-        <v>8</v>
-      </c>
-      <c r="P267">
-        <v>3</v>
-      </c>
-      <c r="Q267">
-        <v>4</v>
-      </c>
-      <c r="R267">
+        <v>1</v>
+      </c>
+      <c r="T267">
+        <v>1</v>
+      </c>
+      <c r="U267">
+        <v>3</v>
+      </c>
+      <c r="V267">
+        <v>36</v>
+      </c>
+      <c r="W267">
+        <v>43</v>
+      </c>
+      <c r="X267">
+        <v>18</v>
+      </c>
+      <c r="Y267">
+        <v>17</v>
+      </c>
+      <c r="Z267">
         <v>2</v>
       </c>
     </row>
     <row r="268" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A268">
-        <v>201470</v>
+        <v>201453</v>
       </c>
       <c r="B268" t="s">
         <v>320</v>
       </c>
-      <c r="C268">
-        <v>216</v>
+      <c r="C268" s="3">
+        <v>1005</v>
       </c>
       <c r="D268" s="1">
-        <v>45652</v>
+        <v>45842</v>
       </c>
       <c r="E268">
-        <v>181</v>
+        <v>955</v>
       </c>
       <c r="F268" s="2">
-        <v>0.83799999999999997</v>
+        <v>0.95020000000000004</v>
+      </c>
+      <c r="G268">
+        <v>1</v>
+      </c>
+      <c r="H268">
+        <v>264</v>
+      </c>
+      <c r="I268">
+        <v>326</v>
       </c>
       <c r="J268">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="K268">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="L268">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="M268">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N268">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="O268">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P268">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q268">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R268">
-        <v>7</v>
-      </c>
-      <c r="S268">
-        <v>1</v>
-      </c>
-      <c r="U268">
-        <v>4</v>
-      </c>
-      <c r="V268">
-        <v>27</v>
-      </c>
-      <c r="W268">
-        <v>18</v>
-      </c>
-      <c r="X268">
-        <v>17</v>
-      </c>
-      <c r="Y268">
         <v>3</v>
       </c>
     </row>
     <row r="269" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A269">
+        <v>201470</v>
+      </c>
       <c r="B269" t="s">
         <v>321</v>
       </c>
-      <c r="C269" s="3">
-        <v>141071</v>
-      </c>
-      <c r="E269" s="3">
-        <v>128577</v>
+      <c r="C269">
+        <v>216</v>
+      </c>
+      <c r="D269" s="1">
+        <v>45652</v>
+      </c>
+      <c r="E269">
+        <v>184</v>
       </c>
       <c r="F269" s="2">
-        <v>0.91139999999999999</v>
-      </c>
-      <c r="G269" s="3">
-        <v>1088</v>
-      </c>
-      <c r="H269" s="3">
-        <v>12134</v>
-      </c>
-      <c r="I269" s="3">
-        <v>26697</v>
-      </c>
-      <c r="J269" s="3">
-        <v>30968</v>
-      </c>
-      <c r="K269" s="3">
-        <v>18669</v>
-      </c>
-      <c r="L269" s="3">
-        <v>11221</v>
-      </c>
-      <c r="M269" s="3">
-        <v>6141</v>
-      </c>
-      <c r="N269" s="3">
-        <v>3973</v>
-      </c>
-      <c r="O269" s="3">
-        <v>3319</v>
-      </c>
-      <c r="P269" s="3">
-        <v>2821</v>
-      </c>
-      <c r="Q269" s="3">
-        <v>1465</v>
-      </c>
-      <c r="R269" s="3">
-        <v>1259</v>
-      </c>
-      <c r="S269" s="3">
-        <v>1337</v>
-      </c>
-      <c r="T269" s="3">
-        <v>1480</v>
+        <v>0.85189999999999999</v>
+      </c>
+      <c r="J269">
+        <v>1</v>
+      </c>
+      <c r="K269">
+        <v>23</v>
+      </c>
+      <c r="L269">
+        <v>30</v>
+      </c>
+      <c r="M269">
+        <v>26</v>
+      </c>
+      <c r="N269">
+        <v>17</v>
+      </c>
+      <c r="O269">
+        <v>3</v>
+      </c>
+      <c r="P269">
+        <v>2</v>
+      </c>
+      <c r="Q269">
+        <v>2</v>
+      </c>
+      <c r="R269">
+        <v>7</v>
+      </c>
+      <c r="S269">
+        <v>1</v>
       </c>
       <c r="U269">
-        <v>973</v>
+        <v>4</v>
       </c>
       <c r="V269">
-        <v>633</v>
+        <v>27</v>
       </c>
       <c r="W269">
-        <v>604</v>
+        <v>18</v>
       </c>
       <c r="X269">
-        <v>414</v>
+        <v>17</v>
       </c>
       <c r="Y269">
-        <v>310</v>
-      </c>
-      <c r="Z269">
-        <v>575</v>
-      </c>
-      <c r="AA269">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="270" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="B270" t="s">
+        <v>322</v>
+      </c>
+      <c r="C270" s="3">
+        <v>141271</v>
+      </c>
+      <c r="E270" s="3">
+        <v>129485</v>
+      </c>
+      <c r="F270" s="2">
+        <v>0.91659999999999997</v>
+      </c>
+      <c r="G270" s="3">
+        <v>1096</v>
+      </c>
+      <c r="H270" s="3">
+        <v>12146</v>
+      </c>
+      <c r="I270" s="3">
+        <v>26743</v>
+      </c>
+      <c r="J270" s="3">
+        <v>31107</v>
+      </c>
+      <c r="K270" s="3">
+        <v>18706</v>
+      </c>
+      <c r="L270" s="3">
+        <v>11228</v>
+      </c>
+      <c r="M270" s="3">
+        <v>6412</v>
+      </c>
+      <c r="N270" s="3">
+        <v>4117</v>
+      </c>
+      <c r="O270" s="3">
+        <v>3348</v>
+      </c>
+      <c r="P270" s="3">
+        <v>2841</v>
+      </c>
+      <c r="Q270" s="3">
+        <v>1475</v>
+      </c>
+      <c r="R270" s="3">
+        <v>1277</v>
+      </c>
+      <c r="S270" s="3">
+        <v>1344</v>
+      </c>
+      <c r="T270" s="3">
+        <v>1484</v>
+      </c>
+      <c r="U270">
+        <v>990</v>
+      </c>
+      <c r="V270">
+        <v>655</v>
+      </c>
+      <c r="W270">
+        <v>628</v>
+      </c>
+      <c r="X270">
+        <v>431</v>
+      </c>
+      <c r="Y270">
+        <v>325</v>
+      </c>
+      <c r="Z270">
+        <v>581</v>
+      </c>
+      <c r="AA270">
+        <v>300</v>
+      </c>
+      <c r="AB270">
         <v>288</v>
       </c>
-      <c r="AB269">
-        <v>284</v>
-      </c>
-      <c r="AC269">
+      <c r="AC270">
         <v>400</v>
       </c>
-      <c r="AD269">
-        <v>192</v>
-      </c>
-      <c r="AE269">
-        <v>116</v>
-      </c>
-      <c r="AF269">
-        <v>320</v>
-      </c>
-      <c r="AG269">
-        <v>186</v>
-      </c>
-      <c r="AH269">
-        <v>82</v>
-      </c>
-      <c r="AI269">
-        <v>141</v>
-      </c>
-      <c r="AJ269">
-        <v>44</v>
-      </c>
-      <c r="AK269">
-        <v>47</v>
-      </c>
-      <c r="AL269">
-        <v>40</v>
-      </c>
-      <c r="AM269">
-        <v>47</v>
-      </c>
-      <c r="AN269">
-        <v>59</v>
-      </c>
-      <c r="AO269">
+      <c r="AD270">
+        <v>198</v>
+      </c>
+      <c r="AE270">
+        <v>120</v>
+      </c>
+      <c r="AF270">
+        <v>322</v>
+      </c>
+      <c r="AG270">
+        <v>188</v>
+      </c>
+      <c r="AH270">
+        <v>84</v>
+      </c>
+      <c r="AI270">
+        <v>144</v>
+      </c>
+      <c r="AJ270">
+        <v>46</v>
+      </c>
+      <c r="AK270">
+        <v>48</v>
+      </c>
+      <c r="AL270">
+        <v>41</v>
+      </c>
+      <c r="AM270">
+        <v>51</v>
+      </c>
+      <c r="AN270">
+        <v>64</v>
+      </c>
+      <c r="AO270">
         <v>26</v>
       </c>
-      <c r="AP269">
+      <c r="AP270">
+        <v>24</v>
+      </c>
+      <c r="AQ270">
+        <v>29</v>
+      </c>
+      <c r="AR270">
+        <v>26</v>
+      </c>
+      <c r="AS270">
+        <v>38</v>
+      </c>
+      <c r="AT270">
+        <v>22</v>
+      </c>
+      <c r="AU270">
+        <v>19</v>
+      </c>
+      <c r="AV270">
         <v>23</v>
       </c>
-      <c r="AQ269">
-        <v>29</v>
-      </c>
-      <c r="AR269">
-        <v>26</v>
-      </c>
-      <c r="AS269">
-        <v>38</v>
-      </c>
-      <c r="AT269">
-        <v>22</v>
-      </c>
-      <c r="AU269">
-        <v>16</v>
-      </c>
-      <c r="AV269">
-        <v>21</v>
-      </c>
-      <c r="AW269">
+      <c r="AW270">
+        <v>12</v>
+      </c>
+      <c r="AX270">
+        <v>6</v>
+      </c>
+      <c r="AY270">
         <v>11</v>
       </c>
-      <c r="AX269">
+      <c r="AZ270">
+        <v>13</v>
+      </c>
+      <c r="BA270">
         <v>6</v>
       </c>
-      <c r="AY269">
-        <v>11</v>
-      </c>
-      <c r="AZ269">
-        <v>13</v>
-      </c>
-      <c r="BA269">
-        <v>6</v>
-      </c>
-      <c r="BB269">
+      <c r="BB270">
         <v>2</v>
       </c>
     </row>
